--- a/BackEnd/student_schedule_output.xlsx
+++ b/BackEnd/student_schedule_output.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Student Schedule" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Student Schedule'!$A$1:$G$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Student Schedule'!$A$1:$G$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -743,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -835,7 +835,7 @@
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>3A</t>
+          <t>1C</t>
         </is>
       </c>
     </row>
@@ -891,9 +891,9 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>SIA
-Jerahmeel Cantos
-Room 1
+          <t>101
+Mylen P
+Room 5
 [Lecture]</t>
         </is>
       </c>
@@ -1085,12 +1085,267 @@
       <c r="F27" s="1" t="n"/>
       <c r="G27" s="1" t="n"/>
     </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>3A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Total: 1 hr   |   Lecture: 1 hr (1 slot)   |   Laboratory: 0 hrs (0 slots)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>TIME</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="52" customHeight="1">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>8:00 AM - 9:00 AM</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>SIA
+Jerahmeel Cantos
+Room 1
+[Lecture]</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="n"/>
+      <c r="D31" s="15" t="n"/>
+      <c r="E31" s="15" t="n"/>
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="15" t="n"/>
+    </row>
+    <row r="32" ht="52" customHeight="1">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>9:00 AM - 10:00 AM</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="n"/>
+      <c r="C32" s="15" t="n"/>
+      <c r="D32" s="15" t="n"/>
+      <c r="E32" s="15" t="n"/>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="15" t="n"/>
+    </row>
+    <row r="33" ht="52" customHeight="1">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>10:00 AM - 11:00 AM</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="n"/>
+      <c r="C33" s="15" t="n"/>
+      <c r="D33" s="15" t="n"/>
+      <c r="E33" s="15" t="n"/>
+      <c r="F33" s="15" t="n"/>
+      <c r="G33" s="15" t="n"/>
+    </row>
+    <row r="34" ht="52" customHeight="1">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>11:00 AM - 12:00 PM</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="n"/>
+      <c r="C34" s="15" t="n"/>
+      <c r="D34" s="15" t="n"/>
+      <c r="E34" s="15" t="n"/>
+      <c r="F34" s="15" t="n"/>
+      <c r="G34" s="15" t="n"/>
+    </row>
+    <row r="35" ht="52" customHeight="1">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>12:00 PM - 1:00 PM</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="n"/>
+      <c r="C35" s="15" t="n"/>
+      <c r="D35" s="15" t="n"/>
+      <c r="E35" s="15" t="n"/>
+      <c r="F35" s="15" t="n"/>
+      <c r="G35" s="15" t="n"/>
+    </row>
+    <row r="36" ht="52" customHeight="1">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>1:00 PM - 2:00 PM</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="n"/>
+      <c r="C36" s="15" t="n"/>
+      <c r="D36" s="15" t="n"/>
+      <c r="E36" s="15" t="n"/>
+      <c r="F36" s="15" t="n"/>
+      <c r="G36" s="15" t="n"/>
+    </row>
+    <row r="37" ht="52" customHeight="1">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>2:00 PM - 3:00 PM</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="n"/>
+      <c r="C37" s="15" t="n"/>
+      <c r="D37" s="15" t="n"/>
+      <c r="E37" s="15" t="n"/>
+      <c r="F37" s="15" t="n"/>
+      <c r="G37" s="15" t="n"/>
+    </row>
+    <row r="38" ht="52" customHeight="1">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>3:00 PM - 4:00 PM</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="n"/>
+      <c r="C38" s="15" t="n"/>
+      <c r="D38" s="15" t="n"/>
+      <c r="E38" s="15" t="n"/>
+      <c r="F38" s="15" t="n"/>
+      <c r="G38" s="15" t="n"/>
+    </row>
+    <row r="39" ht="52" customHeight="1">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>4:00 PM - 5:00 PM</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="n"/>
+      <c r="C39" s="15" t="n"/>
+      <c r="D39" s="15" t="n"/>
+      <c r="E39" s="15" t="n"/>
+      <c r="F39" s="15" t="n"/>
+      <c r="G39" s="15" t="n"/>
+    </row>
+    <row r="40" ht="52" customHeight="1">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>5:00 PM - 6:00 PM</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="n"/>
+      <c r="C40" s="15" t="n"/>
+      <c r="D40" s="15" t="n"/>
+      <c r="E40" s="15" t="n"/>
+      <c r="F40" s="15" t="n"/>
+      <c r="G40" s="15" t="n"/>
+    </row>
+    <row r="41" ht="52" customHeight="1">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>6:00 PM - 7:00 PM</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="n"/>
+      <c r="C41" s="15" t="n"/>
+      <c r="D41" s="15" t="n"/>
+      <c r="E41" s="15" t="n"/>
+      <c r="F41" s="15" t="n"/>
+      <c r="G41" s="15" t="n"/>
+    </row>
+    <row r="42" ht="52" customHeight="1">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>7:00 PM - 8:00 PM</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="n"/>
+      <c r="C42" s="15" t="n"/>
+      <c r="D42" s="15" t="n"/>
+      <c r="E42" s="15" t="n"/>
+      <c r="F42" s="15" t="n"/>
+      <c r="G42" s="15" t="n"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>Legend:</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Laboratory</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Lecture Room</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="n"/>
+      <c r="E43" s="1" t="n"/>
+      <c r="F43" s="1" t="n"/>
+      <c r="G43" s="1" t="n"/>
+    </row>
+    <row r="44" ht="14" customHeight="1">
+      <c r="A44" s="19" t="n"/>
+      <c r="B44" s="19" t="n"/>
+      <c r="C44" s="19" t="n"/>
+      <c r="D44" s="19" t="n"/>
+      <c r="E44" s="19" t="n"/>
+      <c r="F44" s="19" t="n"/>
+      <c r="G44" s="19" t="n"/>
+    </row>
+    <row r="45" ht="10" customHeight="1">
+      <c r="A45" s="1" t="n"/>
+      <c r="B45" s="1" t="n"/>
+      <c r="C45" s="1" t="n"/>
+      <c r="D45" s="1" t="n"/>
+      <c r="E45" s="1" t="n"/>
+      <c r="F45" s="1" t="n"/>
+      <c r="G45" s="1" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="9">
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A29:G29"/>
     <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A28:G28"/>
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A10:G10"/>
     <mergeCell ref="A5:G5"/>
